--- a/Speciallægeloft/speciallægeloft_data/Region_Midt.xlsx
+++ b/Speciallægeloft/speciallægeloft_data/Region_Midt.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="46">
   <si>
     <t xml:space="preserve">Antal ansatte - 002 - </t>
   </si>
@@ -19,42 +19,42 @@
     <t/>
   </si>
   <si>
+    <t>dec 2024</t>
+  </si>
+  <si>
+    <t>jan 2025</t>
+  </si>
+  <si>
+    <t>feb 2025</t>
+  </si>
+  <si>
+    <t>mar 2025</t>
+  </si>
+  <si>
+    <t>apr 2025</t>
+  </si>
+  <si>
+    <t>maj 2025</t>
+  </si>
+  <si>
+    <t>jun 2025</t>
+  </si>
+  <si>
+    <t>jul 2025</t>
+  </si>
+  <si>
+    <t>aug 2025</t>
+  </si>
+  <si>
+    <t>sep 2025</t>
+  </si>
+  <si>
+    <t>okt 2025</t>
+  </si>
+  <si>
     <t>nov 2025</t>
   </si>
   <si>
-    <t>okt 2025</t>
-  </si>
-  <si>
-    <t>sep 2025</t>
-  </si>
-  <si>
-    <t>aug 2025</t>
-  </si>
-  <si>
-    <t>jul 2025</t>
-  </si>
-  <si>
-    <t>jun 2025</t>
-  </si>
-  <si>
-    <t>maj 2025</t>
-  </si>
-  <si>
-    <t>apr 2025</t>
-  </si>
-  <si>
-    <t>mar 2025</t>
-  </si>
-  <si>
-    <t>feb 2025</t>
-  </si>
-  <si>
-    <t>jan 2025</t>
-  </si>
-  <si>
-    <t>dec 2024</t>
-  </si>
-  <si>
     <t>Organisation niveau 1</t>
   </si>
   <si>
@@ -85,13 +85,10 @@
     <t>Lokale Løndata</t>
   </si>
   <si>
-    <t>Datasæt 11 2025</t>
-  </si>
-  <si>
-    <t>Kørsel 15.4.2026 13.28.55</t>
-  </si>
-  <si>
-    <t>Gruppe: Region midt</t>
+    <t>Datasæt 12 2024</t>
+  </si>
+  <si>
+    <t>Kørsel 15.4.2026 14.35.15</t>
   </si>
   <si>
     <t>Undergrænse: 5</t>
@@ -597,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -708,40 +705,40 @@
         <v>16</v>
       </c>
       <c r="B4" s="6">
+        <v>931</v>
+      </c>
+      <c r="C4" s="6">
+        <v>944</v>
+      </c>
+      <c r="D4" s="6">
+        <v>951</v>
+      </c>
+      <c r="E4" s="6">
+        <v>957</v>
+      </c>
+      <c r="F4" s="6">
+        <v>957</v>
+      </c>
+      <c r="G4" s="6">
+        <v>955</v>
+      </c>
+      <c r="H4" s="6">
+        <v>962</v>
+      </c>
+      <c r="I4" s="6">
+        <v>963</v>
+      </c>
+      <c r="J4" s="6">
+        <v>961</v>
+      </c>
+      <c r="K4" s="6">
+        <v>973</v>
+      </c>
+      <c r="L4" s="6">
+        <v>971</v>
+      </c>
+      <c r="M4" s="6">
         <v>987</v>
-      </c>
-      <c r="C4" s="6">
-        <v>971</v>
-      </c>
-      <c r="D4" s="6">
-        <v>973</v>
-      </c>
-      <c r="E4" s="6">
-        <v>961</v>
-      </c>
-      <c r="F4" s="6">
-        <v>963</v>
-      </c>
-      <c r="G4" s="6">
-        <v>962</v>
-      </c>
-      <c r="H4" s="6">
-        <v>955</v>
-      </c>
-      <c r="I4" s="6">
-        <v>957</v>
-      </c>
-      <c r="J4" s="6">
-        <v>957</v>
-      </c>
-      <c r="K4" s="6">
-        <v>951</v>
-      </c>
-      <c r="L4" s="6">
-        <v>944</v>
-      </c>
-      <c r="M4" s="6">
-        <v>931</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -749,40 +746,40 @@
         <v>17</v>
       </c>
       <c r="B5" s="8">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C5" s="8">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D5" s="8">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E5" s="8">
         <v>339</v>
       </c>
       <c r="F5" s="8">
+        <v>335</v>
+      </c>
+      <c r="G5" s="8">
+        <v>335</v>
+      </c>
+      <c r="H5" s="8">
+        <v>336</v>
+      </c>
+      <c r="I5" s="8">
         <v>337</v>
-      </c>
-      <c r="G5" s="8">
-        <v>336</v>
-      </c>
-      <c r="H5" s="8">
-        <v>335</v>
-      </c>
-      <c r="I5" s="8">
-        <v>335</v>
       </c>
       <c r="J5" s="8">
         <v>339</v>
       </c>
       <c r="K5" s="8">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="L5" s="8">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M5" s="8">
-        <v>331</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -790,40 +787,40 @@
         <v>18</v>
       </c>
       <c r="B6" s="6">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C6" s="6">
         <v>310</v>
       </c>
       <c r="D6" s="6">
+        <v>308</v>
+      </c>
+      <c r="E6" s="6">
+        <v>309</v>
+      </c>
+      <c r="F6" s="6">
+        <v>305</v>
+      </c>
+      <c r="G6" s="6">
+        <v>304</v>
+      </c>
+      <c r="H6" s="6">
+        <v>309</v>
+      </c>
+      <c r="I6" s="6">
+        <v>312</v>
+      </c>
+      <c r="J6" s="6">
+        <v>308</v>
+      </c>
+      <c r="K6" s="6">
         <v>313</v>
-      </c>
-      <c r="E6" s="6">
-        <v>308</v>
-      </c>
-      <c r="F6" s="6">
-        <v>312</v>
-      </c>
-      <c r="G6" s="6">
-        <v>309</v>
-      </c>
-      <c r="H6" s="6">
-        <v>304</v>
-      </c>
-      <c r="I6" s="6">
-        <v>305</v>
-      </c>
-      <c r="J6" s="6">
-        <v>309</v>
-      </c>
-      <c r="K6" s="6">
-        <v>308</v>
       </c>
       <c r="L6" s="6">
         <v>310</v>
       </c>
       <c r="M6" s="6">
-        <v>305</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -831,40 +828,40 @@
         <v>19</v>
       </c>
       <c r="B7" s="8">
+        <v>132</v>
+      </c>
+      <c r="C7" s="8">
+        <v>138</v>
+      </c>
+      <c r="D7" s="8">
+        <v>140</v>
+      </c>
+      <c r="E7" s="8">
+        <v>144</v>
+      </c>
+      <c r="F7" s="8">
+        <v>149</v>
+      </c>
+      <c r="G7" s="8">
+        <v>146</v>
+      </c>
+      <c r="H7" s="8">
+        <v>147</v>
+      </c>
+      <c r="I7" s="8">
+        <v>146</v>
+      </c>
+      <c r="J7" s="8">
+        <v>148</v>
+      </c>
+      <c r="K7" s="8">
+        <v>149</v>
+      </c>
+      <c r="L7" s="8">
+        <v>149</v>
+      </c>
+      <c r="M7" s="8">
         <v>153</v>
-      </c>
-      <c r="C7" s="8">
-        <v>149</v>
-      </c>
-      <c r="D7" s="8">
-        <v>149</v>
-      </c>
-      <c r="E7" s="8">
-        <v>148</v>
-      </c>
-      <c r="F7" s="8">
-        <v>146</v>
-      </c>
-      <c r="G7" s="8">
-        <v>147</v>
-      </c>
-      <c r="H7" s="8">
-        <v>146</v>
-      </c>
-      <c r="I7" s="8">
-        <v>149</v>
-      </c>
-      <c r="J7" s="8">
-        <v>144</v>
-      </c>
-      <c r="K7" s="8">
-        <v>140</v>
-      </c>
-      <c r="L7" s="8">
-        <v>138</v>
-      </c>
-      <c r="M7" s="8">
-        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -872,16 +869,16 @@
         <v>20</v>
       </c>
       <c r="B8" s="6">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C8" s="6">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D8" s="6">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E8" s="6">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F8" s="6">
         <v>168</v>
@@ -896,16 +893,16 @@
         <v>168</v>
       </c>
       <c r="J8" s="6">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K8" s="6">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="L8" s="6">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M8" s="6">
-        <v>163</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -944,46 +941,52 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
+      <c r="B19" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
         <v>30</v>
       </c>
-      <c r="B23" t="s">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -991,31 +994,31 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>1</v>
-      </c>
-      <c r="B28" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B29" t="s">
-        <v>20</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1031,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="B33" t="s">
-        <v>1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1039,63 +1042,47 @@
         <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>1</v>
-      </c>
-      <c r="B35" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
         <v>40</v>
       </c>
-      <c r="B38" t="s">
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>1</v>
+      </c>
+      <c r="B37" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>1</v>
-      </c>
-      <c r="B42" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>1</v>
-      </c>
-      <c r="B43" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
